--- a/Data/EXCEL/Transfer/salemon/202208/3712-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/3712-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{065C9CD5-CD0D-4966-A163-4CA274C26BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6165CB6E-C5F4-4B24-9067-7281759D1389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="3712-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,15 +1226,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="5" width="9.875" customWidth="1"/>
-    <col min="6" max="6" width="10.75" customWidth="1"/>
-    <col min="7" max="7" width="11.25" customWidth="1"/>
-    <col min="8" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="10.375" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1379,1907 +1387,1907 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>31.6</v>
+        <v>29</v>
       </c>
       <c r="C5" s="7">
-        <v>29.15</v>
+        <v>28.75</v>
       </c>
       <c r="D5" s="7">
-        <v>31.85</v>
+        <v>29.3</v>
       </c>
       <c r="E5" s="7">
-        <v>27.3</v>
+        <v>26.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-2.35</v>
+        <v>-0.4</v>
       </c>
       <c r="G5" s="8">
-        <v>-7.46</v>
+        <v>-1.37</v>
       </c>
       <c r="H5" s="9">
-        <v>6.37</v>
-      </c>
-      <c r="I5" s="8">
-        <v>-35.5</v>
-      </c>
-      <c r="J5" s="8">
-        <v>-6.38</v>
+        <v>8.16</v>
+      </c>
+      <c r="I5" s="10">
+        <v>28</v>
+      </c>
+      <c r="J5" s="10">
+        <v>11.3</v>
       </c>
       <c r="K5" s="9">
-        <v>63.26</v>
+        <v>71.42</v>
       </c>
       <c r="L5" s="10">
-        <v>37.9</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M5" s="9">
-        <v>6.37</v>
-      </c>
-      <c r="N5" s="8">
-        <v>-35.5</v>
-      </c>
-      <c r="O5" s="8">
-        <v>-6.38</v>
+        <v>8.16</v>
+      </c>
+      <c r="N5" s="10">
+        <v>28</v>
+      </c>
+      <c r="O5" s="10">
+        <v>11.3</v>
       </c>
       <c r="P5" s="9">
-        <v>63.26</v>
+        <v>71.42</v>
       </c>
       <c r="Q5" s="10">
-        <v>37.9</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>30.75</v>
+        <v>31.6</v>
       </c>
       <c r="C6" s="7">
-        <v>31.5</v>
+        <v>29.15</v>
       </c>
       <c r="D6" s="7">
-        <v>32.35</v>
+        <v>31.85</v>
       </c>
       <c r="E6" s="7">
-        <v>29.55</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0.65</v>
-      </c>
-      <c r="G6" s="10">
-        <v>2.11</v>
+        <v>27.3</v>
+      </c>
+      <c r="F6" s="8">
+        <v>-2.35</v>
+      </c>
+      <c r="G6" s="8">
+        <v>-7.46</v>
       </c>
       <c r="H6" s="9">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="I6" s="10">
-        <v>7.66</v>
-      </c>
-      <c r="J6" s="10">
-        <v>51.3</v>
+        <v>6.37</v>
+      </c>
+      <c r="I6" s="8">
+        <v>-35.5</v>
+      </c>
+      <c r="J6" s="8">
+        <v>-6.38</v>
       </c>
       <c r="K6" s="9">
-        <v>56.89</v>
+        <v>63.26</v>
       </c>
       <c r="L6" s="10">
-        <v>45.6</v>
+        <v>37.9</v>
       </c>
       <c r="M6" s="9">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="N6" s="10">
-        <v>7.66</v>
-      </c>
-      <c r="O6" s="10">
-        <v>51.3</v>
+        <v>6.37</v>
+      </c>
+      <c r="N6" s="8">
+        <v>-35.5</v>
+      </c>
+      <c r="O6" s="8">
+        <v>-6.38</v>
       </c>
       <c r="P6" s="9">
-        <v>56.89</v>
+        <v>63.26</v>
       </c>
       <c r="Q6" s="10">
-        <v>45.6</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>34.75</v>
+        <v>30.75</v>
       </c>
       <c r="C7" s="7">
-        <v>30.85</v>
+        <v>31.5</v>
       </c>
       <c r="D7" s="7">
-        <v>35.049999999999997</v>
+        <v>32.35</v>
       </c>
       <c r="E7" s="7">
-        <v>29.3</v>
-      </c>
-      <c r="F7" s="8">
-        <v>-3.75</v>
-      </c>
-      <c r="G7" s="8">
-        <v>-10.84</v>
+        <v>29.55</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.65</v>
+      </c>
+      <c r="G7" s="10">
+        <v>2.11</v>
       </c>
       <c r="H7" s="9">
-        <v>9.18</v>
-      </c>
-      <c r="I7" s="8">
-        <v>-22.9</v>
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="I7" s="10">
+        <v>7.66</v>
       </c>
       <c r="J7" s="10">
-        <v>74.5</v>
+        <v>51.3</v>
       </c>
       <c r="K7" s="9">
-        <v>47.01</v>
+        <v>56.89</v>
       </c>
       <c r="L7" s="10">
-        <v>44.4</v>
+        <v>45.6</v>
       </c>
       <c r="M7" s="9">
-        <v>9.18</v>
-      </c>
-      <c r="N7" s="8">
-        <v>-22.9</v>
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="N7" s="10">
+        <v>7.66</v>
       </c>
       <c r="O7" s="10">
-        <v>74.5</v>
+        <v>51.3</v>
       </c>
       <c r="P7" s="9">
-        <v>47.01</v>
+        <v>56.89</v>
       </c>
       <c r="Q7" s="10">
-        <v>44.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>30.75</v>
+        <v>34.75</v>
       </c>
       <c r="C8" s="7">
-        <v>34.6</v>
+        <v>30.85</v>
       </c>
       <c r="D8" s="7">
-        <v>35.200000000000003</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="E8" s="7">
-        <v>29.8</v>
-      </c>
-      <c r="F8" s="10">
-        <v>3.85</v>
-      </c>
-      <c r="G8" s="10">
-        <v>12.52</v>
+        <v>29.3</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-3.75</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-10.84</v>
       </c>
       <c r="H8" s="9">
-        <v>11.91</v>
-      </c>
-      <c r="I8" s="10">
-        <v>21.2</v>
+        <v>9.18</v>
+      </c>
+      <c r="I8" s="8">
+        <v>-22.9</v>
       </c>
       <c r="J8" s="10">
-        <v>140.5</v>
+        <v>74.5</v>
       </c>
       <c r="K8" s="9">
-        <v>37.83</v>
+        <v>47.01</v>
       </c>
       <c r="L8" s="10">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
       <c r="M8" s="9">
-        <v>11.91</v>
-      </c>
-      <c r="N8" s="10">
-        <v>21.2</v>
+        <v>9.18</v>
+      </c>
+      <c r="N8" s="8">
+        <v>-22.9</v>
       </c>
       <c r="O8" s="10">
-        <v>140.5</v>
+        <v>74.5</v>
       </c>
       <c r="P8" s="9">
-        <v>37.83</v>
+        <v>47.01</v>
       </c>
       <c r="Q8" s="10">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>30.6</v>
+        <v>30.75</v>
       </c>
       <c r="C9" s="7">
-        <v>30.75</v>
+        <v>34.6</v>
       </c>
       <c r="D9" s="7">
-        <v>32.35</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="E9" s="7">
-        <v>29.85</v>
+        <v>29.8</v>
       </c>
       <c r="F9" s="10">
-        <v>0.15</v>
+        <v>3.85</v>
       </c>
       <c r="G9" s="10">
-        <v>0.49</v>
+        <v>12.52</v>
       </c>
       <c r="H9" s="9">
-        <v>9.83</v>
+        <v>11.91</v>
       </c>
       <c r="I9" s="10">
-        <v>19.8</v>
-      </c>
-      <c r="J9" s="8">
-        <v>-6.18</v>
+        <v>21.2</v>
+      </c>
+      <c r="J9" s="10">
+        <v>140.5</v>
       </c>
       <c r="K9" s="9">
-        <v>25.92</v>
+        <v>37.83</v>
       </c>
       <c r="L9" s="10">
-        <v>16</v>
+        <v>38.6</v>
       </c>
       <c r="M9" s="9">
-        <v>9.83</v>
+        <v>11.91</v>
       </c>
       <c r="N9" s="10">
-        <v>19.8</v>
-      </c>
-      <c r="O9" s="8">
-        <v>-6.18</v>
+        <v>21.2</v>
+      </c>
+      <c r="O9" s="10">
+        <v>140.5</v>
       </c>
       <c r="P9" s="9">
-        <v>25.92</v>
+        <v>37.83</v>
       </c>
       <c r="Q9" s="10">
-        <v>16</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>31.15</v>
+        <v>30.6</v>
       </c>
       <c r="C10" s="7">
-        <v>30.6</v>
+        <v>30.75</v>
       </c>
       <c r="D10" s="7">
-        <v>33.1</v>
+        <v>32.35</v>
       </c>
       <c r="E10" s="7">
-        <v>30.3</v>
-      </c>
-      <c r="F10" s="8">
-        <v>-0.25</v>
-      </c>
-      <c r="G10" s="8">
-        <v>-0.81</v>
+        <v>29.85</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.49</v>
       </c>
       <c r="H10" s="9">
-        <v>8.1999999999999993</v>
+        <v>9.83</v>
       </c>
       <c r="I10" s="10">
-        <v>4.03</v>
-      </c>
-      <c r="J10" s="10">
-        <v>59.1</v>
+        <v>19.8</v>
+      </c>
+      <c r="J10" s="8">
+        <v>-6.18</v>
       </c>
       <c r="K10" s="9">
-        <v>16.09</v>
+        <v>25.92</v>
       </c>
       <c r="L10" s="10">
-        <v>35.700000000000003</v>
+        <v>16</v>
       </c>
       <c r="M10" s="9">
-        <v>8.1999999999999993</v>
+        <v>9.83</v>
       </c>
       <c r="N10" s="10">
-        <v>4.03</v>
-      </c>
-      <c r="O10" s="10">
-        <v>59.1</v>
+        <v>19.8</v>
+      </c>
+      <c r="O10" s="8">
+        <v>-6.18</v>
       </c>
       <c r="P10" s="9">
-        <v>16.09</v>
+        <v>25.92</v>
       </c>
       <c r="Q10" s="10">
-        <v>35.700000000000003</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
+        <v>31.15</v>
+      </c>
+      <c r="C11" s="7">
+        <v>30.6</v>
+      </c>
+      <c r="D11" s="7">
         <v>33.1</v>
       </c>
-      <c r="C11" s="7">
-        <v>30.85</v>
-      </c>
-      <c r="D11" s="7">
-        <v>37.200000000000003</v>
-      </c>
       <c r="E11" s="7">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="F11" s="8">
-        <v>-2</v>
+        <v>-0.25</v>
       </c>
       <c r="G11" s="8">
-        <v>-6.09</v>
+        <v>-0.81</v>
       </c>
       <c r="H11" s="9">
-        <v>7.89</v>
-      </c>
-      <c r="I11" s="8">
-        <v>-64.599999999999994</v>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I11" s="10">
+        <v>4.03</v>
       </c>
       <c r="J11" s="10">
-        <v>17.7</v>
+        <v>59.1</v>
       </c>
       <c r="K11" s="9">
-        <v>7.89</v>
+        <v>16.09</v>
       </c>
       <c r="L11" s="10">
-        <v>17.7</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="M11" s="9">
-        <v>7.89</v>
-      </c>
-      <c r="N11" s="8">
-        <v>-64.599999999999994</v>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N11" s="10">
+        <v>4.03</v>
       </c>
       <c r="O11" s="10">
-        <v>17.7</v>
+        <v>59.1</v>
       </c>
       <c r="P11" s="9">
-        <v>7.89</v>
+        <v>16.09</v>
       </c>
       <c r="Q11" s="10">
-        <v>17.7</v>
+        <v>35.700000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>31.3</v>
+        <v>33.1</v>
       </c>
       <c r="C12" s="7">
-        <v>32.85</v>
+        <v>30.85</v>
       </c>
       <c r="D12" s="7">
-        <v>34.200000000000003</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="E12" s="7">
-        <v>30.45</v>
-      </c>
-      <c r="F12" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="G12" s="10">
-        <v>4.45</v>
+        <v>30.6</v>
+      </c>
+      <c r="F12" s="8">
+        <v>-2</v>
+      </c>
+      <c r="G12" s="8">
+        <v>-6.09</v>
       </c>
       <c r="H12" s="9">
-        <v>22.29</v>
-      </c>
-      <c r="I12" s="10">
-        <v>49.9</v>
+        <v>7.89</v>
+      </c>
+      <c r="I12" s="8">
+        <v>-64.599999999999994</v>
       </c>
       <c r="J12" s="10">
-        <v>149</v>
+        <v>17.7</v>
       </c>
       <c r="K12" s="9">
-        <v>112.4</v>
+        <v>7.89</v>
       </c>
       <c r="L12" s="10">
-        <v>60.8</v>
+        <v>17.7</v>
       </c>
       <c r="M12" s="9">
-        <v>22.29</v>
-      </c>
-      <c r="N12" s="10">
-        <v>49.9</v>
+        <v>7.89</v>
+      </c>
+      <c r="N12" s="8">
+        <v>-64.599999999999994</v>
       </c>
       <c r="O12" s="10">
-        <v>149</v>
+        <v>17.7</v>
       </c>
       <c r="P12" s="9">
-        <v>112.4</v>
+        <v>7.89</v>
       </c>
       <c r="Q12" s="10">
-        <v>60.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>33.6</v>
+        <v>31.3</v>
       </c>
       <c r="C13" s="7">
-        <v>31.45</v>
+        <v>32.85</v>
       </c>
       <c r="D13" s="7">
-        <v>37.299999999999997</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="E13" s="7">
-        <v>30.15</v>
-      </c>
-      <c r="F13" s="8">
-        <v>-1.85</v>
-      </c>
-      <c r="G13" s="8">
-        <v>-5.56</v>
+        <v>30.45</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="G13" s="10">
+        <v>4.45</v>
       </c>
       <c r="H13" s="9">
-        <v>14.87</v>
+        <v>22.29</v>
       </c>
       <c r="I13" s="10">
-        <v>18</v>
+        <v>49.9</v>
       </c>
       <c r="J13" s="10">
-        <v>85.7</v>
+        <v>149</v>
       </c>
       <c r="K13" s="9">
-        <v>90.08</v>
+        <v>112.4</v>
       </c>
       <c r="L13" s="10">
-        <v>47.8</v>
+        <v>60.8</v>
       </c>
       <c r="M13" s="9">
-        <v>14.87</v>
+        <v>22.29</v>
       </c>
       <c r="N13" s="10">
-        <v>18</v>
+        <v>49.9</v>
       </c>
       <c r="O13" s="10">
-        <v>85.7</v>
+        <v>149</v>
       </c>
       <c r="P13" s="9">
-        <v>90.08</v>
+        <v>112.4</v>
       </c>
       <c r="Q13" s="10">
-        <v>47.8</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>36.9</v>
+        <v>33.6</v>
       </c>
       <c r="C14" s="7">
-        <v>33.299999999999997</v>
+        <v>31.45</v>
       </c>
       <c r="D14" s="7">
-        <v>38.549999999999997</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="E14" s="7">
-        <v>31.6</v>
+        <v>30.15</v>
       </c>
       <c r="F14" s="8">
-        <v>-2.75</v>
+        <v>-1.85</v>
       </c>
       <c r="G14" s="8">
-        <v>-7.63</v>
+        <v>-5.56</v>
       </c>
       <c r="H14" s="9">
-        <v>12.6</v>
+        <v>14.87</v>
       </c>
       <c r="I14" s="10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J14" s="10">
-        <v>77</v>
+        <v>85.7</v>
       </c>
       <c r="K14" s="9">
-        <v>75.209999999999994</v>
+        <v>90.08</v>
       </c>
       <c r="L14" s="10">
-        <v>42.1</v>
+        <v>47.8</v>
       </c>
       <c r="M14" s="9">
-        <v>12.6</v>
+        <v>14.87</v>
       </c>
       <c r="N14" s="10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="O14" s="10">
-        <v>77</v>
+        <v>85.7</v>
       </c>
       <c r="P14" s="9">
-        <v>75.209999999999994</v>
+        <v>90.08</v>
       </c>
       <c r="Q14" s="10">
-        <v>42.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>31.9</v>
+        <v>36.9</v>
       </c>
       <c r="C15" s="7">
-        <v>36.049999999999997</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="D15" s="7">
-        <v>36.049999999999997</v>
+        <v>38.549999999999997</v>
       </c>
       <c r="E15" s="7">
-        <v>29.75</v>
-      </c>
-      <c r="F15" s="10">
-        <v>4.05</v>
-      </c>
-      <c r="G15" s="10">
-        <v>12.66</v>
+        <v>31.6</v>
+      </c>
+      <c r="F15" s="8">
+        <v>-2.75</v>
+      </c>
+      <c r="G15" s="8">
+        <v>-7.63</v>
       </c>
       <c r="H15" s="9">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="I15" s="10">
-        <v>28.3</v>
+        <v>34</v>
       </c>
       <c r="J15" s="10">
-        <v>48.1</v>
+        <v>77</v>
       </c>
       <c r="K15" s="9">
-        <v>62.61</v>
+        <v>75.209999999999994</v>
       </c>
       <c r="L15" s="10">
-        <v>36.700000000000003</v>
+        <v>42.1</v>
       </c>
       <c r="M15" s="9">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="N15" s="10">
-        <v>28.3</v>
+        <v>34</v>
       </c>
       <c r="O15" s="10">
-        <v>48.1</v>
+        <v>77</v>
       </c>
       <c r="P15" s="9">
-        <v>62.61</v>
+        <v>75.209999999999994</v>
       </c>
       <c r="Q15" s="10">
-        <v>36.700000000000003</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>36.35</v>
+        <v>31.9</v>
       </c>
       <c r="C16" s="7">
-        <v>32</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="D16" s="7">
-        <v>37.35</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="E16" s="7">
-        <v>29.35</v>
-      </c>
-      <c r="F16" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G16" s="8">
-        <v>-11.11</v>
+        <v>29.75</v>
+      </c>
+      <c r="F16" s="10">
+        <v>4.05</v>
+      </c>
+      <c r="G16" s="10">
+        <v>12.66</v>
       </c>
       <c r="H16" s="9">
-        <v>7.33</v>
+        <v>9.4</v>
       </c>
       <c r="I16" s="10">
-        <v>7.64</v>
+        <v>28.3</v>
       </c>
       <c r="J16" s="10">
-        <v>34</v>
+        <v>48.1</v>
       </c>
       <c r="K16" s="9">
-        <v>53.21</v>
+        <v>62.61</v>
       </c>
       <c r="L16" s="10">
-        <v>34.799999999999997</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="M16" s="9">
-        <v>7.33</v>
+        <v>9.4</v>
       </c>
       <c r="N16" s="10">
-        <v>7.64</v>
+        <v>28.3</v>
       </c>
       <c r="O16" s="10">
-        <v>34</v>
+        <v>48.1</v>
       </c>
       <c r="P16" s="9">
-        <v>53.21</v>
+        <v>62.61</v>
       </c>
       <c r="Q16" s="10">
-        <v>34.799999999999997</v>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
-        <v>30.8</v>
+        <v>36.35</v>
       </c>
       <c r="C17" s="7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D17" s="7">
-        <v>42.9</v>
+        <v>37.35</v>
       </c>
       <c r="E17" s="7">
-        <v>30.55</v>
-      </c>
-      <c r="F17" s="10">
-        <v>5.8</v>
-      </c>
-      <c r="G17" s="10">
-        <v>19.21</v>
+        <v>29.35</v>
+      </c>
+      <c r="F17" s="8">
+        <v>-4</v>
+      </c>
+      <c r="G17" s="8">
+        <v>-11.11</v>
       </c>
       <c r="H17" s="9">
-        <v>6.81</v>
+        <v>7.33</v>
       </c>
       <c r="I17" s="10">
-        <v>4.21</v>
+        <v>7.64</v>
       </c>
       <c r="J17" s="10">
-        <v>93.9</v>
+        <v>34</v>
       </c>
       <c r="K17" s="9">
-        <v>45.88</v>
+        <v>53.21</v>
       </c>
       <c r="L17" s="10">
-        <v>35</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="M17" s="9">
-        <v>6.81</v>
+        <v>7.33</v>
       </c>
       <c r="N17" s="10">
-        <v>4.21</v>
+        <v>7.64</v>
       </c>
       <c r="O17" s="10">
-        <v>93.9</v>
+        <v>34</v>
       </c>
       <c r="P17" s="9">
-        <v>45.88</v>
+        <v>53.21</v>
       </c>
       <c r="Q17" s="10">
-        <v>35</v>
+        <v>34.799999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>28.95</v>
+        <v>30.8</v>
       </c>
       <c r="C18" s="7">
-        <v>30.2</v>
+        <v>36</v>
       </c>
       <c r="D18" s="7">
-        <v>30.85</v>
+        <v>42.9</v>
       </c>
       <c r="E18" s="7">
-        <v>27.85</v>
+        <v>30.55</v>
       </c>
       <c r="F18" s="10">
-        <v>1.45</v>
+        <v>5.8</v>
       </c>
       <c r="G18" s="10">
-        <v>5.04</v>
+        <v>19.21</v>
       </c>
       <c r="H18" s="9">
-        <v>6.53</v>
+        <v>6.81</v>
       </c>
       <c r="I18" s="10">
-        <v>24.2</v>
+        <v>4.21</v>
       </c>
       <c r="J18" s="10">
-        <v>75.3</v>
+        <v>93.9</v>
       </c>
       <c r="K18" s="9">
-        <v>39.08</v>
+        <v>45.88</v>
       </c>
       <c r="L18" s="10">
-        <v>28.2</v>
+        <v>35</v>
       </c>
       <c r="M18" s="9">
-        <v>6.53</v>
+        <v>6.81</v>
       </c>
       <c r="N18" s="10">
-        <v>24.2</v>
+        <v>4.21</v>
       </c>
       <c r="O18" s="10">
-        <v>75.3</v>
+        <v>93.9</v>
       </c>
       <c r="P18" s="9">
-        <v>39.08</v>
+        <v>45.88</v>
       </c>
       <c r="Q18" s="10">
-        <v>28.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
-        <v>31.7</v>
+        <v>28.95</v>
       </c>
       <c r="C19" s="7">
-        <v>28.75</v>
+        <v>30.2</v>
       </c>
       <c r="D19" s="7">
-        <v>31.7</v>
+        <v>30.85</v>
       </c>
       <c r="E19" s="7">
-        <v>23.6</v>
-      </c>
-      <c r="F19" s="8">
-        <v>-2.95</v>
-      </c>
-      <c r="G19" s="8">
-        <v>-9.31</v>
+        <v>27.85</v>
+      </c>
+      <c r="F19" s="10">
+        <v>1.45</v>
+      </c>
+      <c r="G19" s="10">
+        <v>5.04</v>
       </c>
       <c r="H19" s="9">
-        <v>5.26</v>
+        <v>6.53</v>
       </c>
       <c r="I19" s="10">
-        <v>6.21</v>
-      </c>
-      <c r="J19" s="8">
-        <v>-2.94</v>
+        <v>24.2</v>
+      </c>
+      <c r="J19" s="10">
+        <v>75.3</v>
       </c>
       <c r="K19" s="9">
-        <v>32.54</v>
+        <v>39.08</v>
       </c>
       <c r="L19" s="10">
-        <v>21.6</v>
+        <v>28.2</v>
       </c>
       <c r="M19" s="9">
-        <v>5.26</v>
+        <v>6.53</v>
       </c>
       <c r="N19" s="10">
-        <v>6.21</v>
-      </c>
-      <c r="O19" s="8">
-        <v>-2.94</v>
+        <v>24.2</v>
+      </c>
+      <c r="O19" s="10">
+        <v>75.3</v>
       </c>
       <c r="P19" s="9">
-        <v>32.54</v>
+        <v>39.08</v>
       </c>
       <c r="Q19" s="10">
-        <v>21.6</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
-        <v>30.05</v>
+        <v>31.7</v>
       </c>
       <c r="C20" s="7">
+        <v>28.75</v>
+      </c>
+      <c r="D20" s="7">
         <v>31.7</v>
       </c>
-      <c r="D20" s="7">
-        <v>35.200000000000003</v>
-      </c>
       <c r="E20" s="7">
-        <v>30</v>
-      </c>
-      <c r="F20" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="G20" s="10">
-        <v>6.02</v>
+        <v>23.6</v>
+      </c>
+      <c r="F20" s="8">
+        <v>-2.95</v>
+      </c>
+      <c r="G20" s="8">
+        <v>-9.31</v>
       </c>
       <c r="H20" s="9">
-        <v>4.95</v>
-      </c>
-      <c r="I20" s="8">
-        <v>-52.7</v>
+        <v>5.26</v>
+      </c>
+      <c r="I20" s="10">
+        <v>6.21</v>
       </c>
       <c r="J20" s="8">
-        <v>-5.14</v>
+        <v>-2.94</v>
       </c>
       <c r="K20" s="9">
-        <v>27.28</v>
+        <v>32.54</v>
       </c>
       <c r="L20" s="10">
-        <v>27.9</v>
+        <v>21.6</v>
       </c>
       <c r="M20" s="9">
-        <v>4.95</v>
-      </c>
-      <c r="N20" s="8">
-        <v>-52.7</v>
+        <v>5.26</v>
+      </c>
+      <c r="N20" s="10">
+        <v>6.21</v>
       </c>
       <c r="O20" s="8">
-        <v>-5.14</v>
+        <v>-2.94</v>
       </c>
       <c r="P20" s="9">
-        <v>27.28</v>
+        <v>32.54</v>
       </c>
       <c r="Q20" s="10">
-        <v>27.9</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>28.9</v>
+        <v>30.05</v>
       </c>
       <c r="C21" s="7">
-        <v>29.9</v>
+        <v>31.7</v>
       </c>
       <c r="D21" s="7">
-        <v>31.2</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="E21" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F21" s="10">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="G21" s="10">
-        <v>3.46</v>
+        <v>6.02</v>
       </c>
       <c r="H21" s="9">
-        <v>10.48</v>
-      </c>
-      <c r="I21" s="10">
-        <v>103.2</v>
-      </c>
-      <c r="J21" s="10">
-        <v>57.4</v>
+        <v>4.95</v>
+      </c>
+      <c r="I21" s="8">
+        <v>-52.7</v>
+      </c>
+      <c r="J21" s="8">
+        <v>-5.14</v>
       </c>
       <c r="K21" s="9">
-        <v>22.33</v>
+        <v>27.28</v>
       </c>
       <c r="L21" s="10">
-        <v>38.6</v>
+        <v>27.9</v>
       </c>
       <c r="M21" s="9">
-        <v>10.48</v>
-      </c>
-      <c r="N21" s="10">
-        <v>103.2</v>
-      </c>
-      <c r="O21" s="10">
-        <v>57.4</v>
+        <v>4.95</v>
+      </c>
+      <c r="N21" s="8">
+        <v>-52.7</v>
+      </c>
+      <c r="O21" s="8">
+        <v>-5.14</v>
       </c>
       <c r="P21" s="9">
-        <v>22.33</v>
+        <v>27.28</v>
       </c>
       <c r="Q21" s="10">
-        <v>38.6</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>25.8</v>
+        <v>28.9</v>
       </c>
       <c r="C22" s="7">
-        <v>28.9</v>
+        <v>29.9</v>
       </c>
       <c r="D22" s="7">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="E22" s="7">
-        <v>24.7</v>
+        <v>28</v>
       </c>
       <c r="F22" s="10">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="G22" s="10">
-        <v>12.02</v>
+        <v>3.46</v>
       </c>
       <c r="H22" s="9">
-        <v>5.16</v>
-      </c>
-      <c r="I22" s="8">
-        <v>-23</v>
+        <v>10.48</v>
+      </c>
+      <c r="I22" s="10">
+        <v>103.2</v>
       </c>
       <c r="J22" s="10">
-        <v>36.700000000000003</v>
+        <v>57.4</v>
       </c>
       <c r="K22" s="9">
-        <v>11.85</v>
+        <v>22.33</v>
       </c>
       <c r="L22" s="10">
-        <v>25.4</v>
+        <v>38.6</v>
       </c>
       <c r="M22" s="9">
-        <v>5.16</v>
-      </c>
-      <c r="N22" s="8">
-        <v>-23</v>
+        <v>10.48</v>
+      </c>
+      <c r="N22" s="10">
+        <v>103.2</v>
       </c>
       <c r="O22" s="10">
-        <v>36.700000000000003</v>
+        <v>57.4</v>
       </c>
       <c r="P22" s="9">
-        <v>11.85</v>
+        <v>22.33</v>
       </c>
       <c r="Q22" s="10">
-        <v>25.4</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>32.4</v>
+        <v>25.8</v>
       </c>
       <c r="C23" s="7">
-        <v>25.8</v>
+        <v>28.9</v>
       </c>
       <c r="D23" s="7">
-        <v>32.9</v>
+        <v>31</v>
       </c>
       <c r="E23" s="7">
-        <v>25</v>
-      </c>
-      <c r="F23" s="8">
-        <v>-6.6</v>
-      </c>
-      <c r="G23" s="8">
-        <v>-20.37</v>
+        <v>24.7</v>
+      </c>
+      <c r="F23" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="G23" s="10">
+        <v>12.02</v>
       </c>
       <c r="H23" s="9">
-        <v>6.7</v>
+        <v>5.16</v>
       </c>
       <c r="I23" s="8">
-        <v>-25.2</v>
+        <v>-23</v>
       </c>
       <c r="J23" s="10">
-        <v>17.8</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="K23" s="9">
-        <v>6.7</v>
+        <v>11.85</v>
       </c>
       <c r="L23" s="10">
-        <v>17.8</v>
+        <v>25.4</v>
       </c>
       <c r="M23" s="9">
-        <v>6.7</v>
+        <v>5.16</v>
       </c>
       <c r="N23" s="8">
-        <v>-25.2</v>
+        <v>-23</v>
       </c>
       <c r="O23" s="10">
-        <v>17.8</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="P23" s="9">
-        <v>6.7</v>
+        <v>11.85</v>
       </c>
       <c r="Q23" s="10">
-        <v>17.8</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>41</v>
+        <v>32.4</v>
       </c>
       <c r="C24" s="7">
-        <v>32.4</v>
+        <v>25.8</v>
       </c>
       <c r="D24" s="7">
-        <v>41.3</v>
+        <v>32.9</v>
       </c>
       <c r="E24" s="7">
-        <v>31.75</v>
+        <v>25</v>
       </c>
       <c r="F24" s="8">
-        <v>-8.1</v>
+        <v>-6.6</v>
       </c>
       <c r="G24" s="8">
-        <v>-20</v>
+        <v>-20.37</v>
       </c>
       <c r="H24" s="9">
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="I24" s="10">
-        <v>11.8</v>
-      </c>
-      <c r="J24" s="8">
-        <v>-3.77</v>
+        <v>6.7</v>
+      </c>
+      <c r="I24" s="8">
+        <v>-25.2</v>
+      </c>
+      <c r="J24" s="10">
+        <v>17.8</v>
       </c>
       <c r="K24" s="9">
-        <v>69.88</v>
-      </c>
-      <c r="L24" s="8">
-        <v>-20.9</v>
+        <v>6.7</v>
+      </c>
+      <c r="L24" s="10">
+        <v>17.8</v>
       </c>
       <c r="M24" s="9">
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="N24" s="10">
-        <v>11.8</v>
-      </c>
-      <c r="O24" s="8">
-        <v>-3.77</v>
+        <v>6.7</v>
+      </c>
+      <c r="N24" s="8">
+        <v>-25.2</v>
+      </c>
+      <c r="O24" s="10">
+        <v>17.8</v>
       </c>
       <c r="P24" s="9">
-        <v>69.88</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>-20.9</v>
+        <v>6.7</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>17.8</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>35.700000000000003</v>
+        <v>41</v>
       </c>
       <c r="C25" s="7">
-        <v>40.5</v>
+        <v>32.4</v>
       </c>
       <c r="D25" s="7">
-        <v>41.75</v>
+        <v>41.3</v>
       </c>
       <c r="E25" s="7">
-        <v>33.1</v>
-      </c>
-      <c r="F25" s="10">
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="G25" s="10">
-        <v>13.6</v>
+        <v>31.75</v>
+      </c>
+      <c r="F25" s="8">
+        <v>-8.1</v>
+      </c>
+      <c r="G25" s="8">
+        <v>-20</v>
       </c>
       <c r="H25" s="9">
-        <v>8</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="I25" s="10">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="J25" s="8">
-        <v>-1.24</v>
+        <v>-3.77</v>
       </c>
       <c r="K25" s="9">
-        <v>60.92</v>
+        <v>69.88</v>
       </c>
       <c r="L25" s="8">
-        <v>-22.9</v>
+        <v>-20.9</v>
       </c>
       <c r="M25" s="9">
-        <v>8</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="N25" s="10">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="O25" s="8">
-        <v>-1.24</v>
+        <v>-3.77</v>
       </c>
       <c r="P25" s="9">
-        <v>60.92</v>
+        <v>69.88</v>
       </c>
       <c r="Q25" s="8">
-        <v>-22.9</v>
+        <v>-20.9</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>38.200000000000003</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="C26" s="7">
-        <v>35.65</v>
+        <v>40.5</v>
       </c>
       <c r="D26" s="7">
-        <v>39.9</v>
+        <v>41.75</v>
       </c>
       <c r="E26" s="7">
-        <v>35.4</v>
-      </c>
-      <c r="F26" s="8">
-        <v>-2.5499999999999998</v>
-      </c>
-      <c r="G26" s="8">
-        <v>-6.68</v>
+        <v>33.1</v>
+      </c>
+      <c r="F26" s="10">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G26" s="10">
+        <v>13.6</v>
       </c>
       <c r="H26" s="9">
-        <v>7.12</v>
+        <v>8</v>
       </c>
       <c r="I26" s="10">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="J26" s="8">
-        <v>-19.7</v>
+        <v>-1.24</v>
       </c>
       <c r="K26" s="9">
-        <v>52.92</v>
+        <v>60.92</v>
       </c>
       <c r="L26" s="8">
-        <v>-25.4</v>
+        <v>-22.9</v>
       </c>
       <c r="M26" s="9">
-        <v>7.12</v>
+        <v>8</v>
       </c>
       <c r="N26" s="10">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="O26" s="8">
-        <v>-19.7</v>
+        <v>-1.24</v>
       </c>
       <c r="P26" s="9">
-        <v>52.92</v>
+        <v>60.92</v>
       </c>
       <c r="Q26" s="8">
-        <v>-25.4</v>
+        <v>-22.9</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>41.35</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="C27" s="7">
-        <v>38.200000000000003</v>
+        <v>35.65</v>
       </c>
       <c r="D27" s="7">
-        <v>44.5</v>
+        <v>39.9</v>
       </c>
       <c r="E27" s="7">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="F27" s="8">
-        <v>-2.2999999999999998</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="G27" s="8">
-        <v>-5.68</v>
+        <v>-6.68</v>
       </c>
       <c r="H27" s="9">
-        <v>6.35</v>
+        <v>7.12</v>
       </c>
       <c r="I27" s="10">
-        <v>16</v>
+        <v>12.2</v>
       </c>
       <c r="J27" s="8">
-        <v>-42.6</v>
+        <v>-19.7</v>
       </c>
       <c r="K27" s="9">
-        <v>45.8</v>
+        <v>52.92</v>
       </c>
       <c r="L27" s="8">
-        <v>-26.2</v>
+        <v>-25.4</v>
       </c>
       <c r="M27" s="9">
-        <v>6.35</v>
+        <v>7.12</v>
       </c>
       <c r="N27" s="10">
-        <v>16</v>
+        <v>12.2</v>
       </c>
       <c r="O27" s="8">
-        <v>-42.6</v>
+        <v>-19.7</v>
       </c>
       <c r="P27" s="9">
-        <v>45.8</v>
+        <v>52.92</v>
       </c>
       <c r="Q27" s="8">
-        <v>-26.2</v>
+        <v>-25.4</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>40.1</v>
+        <v>41.35</v>
       </c>
       <c r="C28" s="7">
-        <v>40.5</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="D28" s="7">
-        <v>44.75</v>
+        <v>44.5</v>
       </c>
       <c r="E28" s="7">
-        <v>35.5</v>
-      </c>
-      <c r="F28" s="10">
-        <v>0.45</v>
-      </c>
-      <c r="G28" s="10">
-        <v>1.1200000000000001</v>
+        <v>35</v>
+      </c>
+      <c r="F28" s="8">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="G28" s="8">
+        <v>-5.68</v>
       </c>
       <c r="H28" s="9">
-        <v>5.47</v>
+        <v>6.35</v>
       </c>
       <c r="I28" s="10">
-        <v>55.8</v>
+        <v>16</v>
       </c>
       <c r="J28" s="8">
-        <v>-10.8</v>
+        <v>-42.6</v>
       </c>
       <c r="K28" s="9">
-        <v>39.46</v>
+        <v>45.8</v>
       </c>
       <c r="L28" s="8">
-        <v>-22.6</v>
+        <v>-26.2</v>
       </c>
       <c r="M28" s="9">
-        <v>5.47</v>
+        <v>6.35</v>
       </c>
       <c r="N28" s="10">
-        <v>55.8</v>
+        <v>16</v>
       </c>
       <c r="O28" s="8">
-        <v>-10.8</v>
+        <v>-42.6</v>
       </c>
       <c r="P28" s="9">
-        <v>39.46</v>
+        <v>45.8</v>
       </c>
       <c r="Q28" s="8">
-        <v>-22.6</v>
+        <v>-26.2</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>33.700000000000003</v>
+        <v>40.1</v>
       </c>
       <c r="C29" s="7">
-        <v>40.049999999999997</v>
+        <v>40.5</v>
       </c>
       <c r="D29" s="7">
-        <v>51.7</v>
+        <v>44.75</v>
       </c>
       <c r="E29" s="7">
-        <v>33.700000000000003</v>
+        <v>35.5</v>
       </c>
       <c r="F29" s="10">
-        <v>7.85</v>
+        <v>0.45</v>
       </c>
       <c r="G29" s="10">
-        <v>24.38</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H29" s="9">
-        <v>3.51</v>
-      </c>
-      <c r="I29" s="8">
-        <v>-5.77</v>
+        <v>5.47</v>
+      </c>
+      <c r="I29" s="10">
+        <v>55.8</v>
       </c>
       <c r="J29" s="8">
-        <v>-47.4</v>
+        <v>-10.8</v>
       </c>
       <c r="K29" s="9">
-        <v>33.99</v>
+        <v>39.46</v>
       </c>
       <c r="L29" s="8">
-        <v>-24.2</v>
+        <v>-22.6</v>
       </c>
       <c r="M29" s="9">
-        <v>3.51</v>
-      </c>
-      <c r="N29" s="8">
-        <v>-5.77</v>
+        <v>5.47</v>
+      </c>
+      <c r="N29" s="10">
+        <v>55.8</v>
       </c>
       <c r="O29" s="8">
-        <v>-47.4</v>
+        <v>-10.8</v>
       </c>
       <c r="P29" s="9">
-        <v>33.99</v>
+        <v>39.46</v>
       </c>
       <c r="Q29" s="8">
-        <v>-24.2</v>
+        <v>-22.6</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>13.8</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="C30" s="7">
-        <v>32.200000000000003</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="D30" s="7">
-        <v>32.450000000000003</v>
+        <v>51.7</v>
       </c>
       <c r="E30" s="7">
-        <v>13.6</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="F30" s="10">
-        <v>18.600000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="G30" s="10">
-        <v>136.76</v>
+        <v>24.38</v>
       </c>
       <c r="H30" s="9">
-        <v>3.73</v>
+        <v>3.51</v>
       </c>
       <c r="I30" s="8">
-        <v>-31.3</v>
+        <v>-5.77</v>
       </c>
       <c r="J30" s="8">
-        <v>-39.9</v>
+        <v>-47.4</v>
       </c>
       <c r="K30" s="9">
-        <v>30.48</v>
+        <v>33.99</v>
       </c>
       <c r="L30" s="8">
-        <v>-20.100000000000001</v>
+        <v>-24.2</v>
       </c>
       <c r="M30" s="9">
-        <v>3.73</v>
+        <v>3.51</v>
       </c>
       <c r="N30" s="8">
-        <v>-31.3</v>
+        <v>-5.77</v>
       </c>
       <c r="O30" s="8">
-        <v>-39.9</v>
+        <v>-47.4</v>
       </c>
       <c r="P30" s="9">
-        <v>30.48</v>
+        <v>33.99</v>
       </c>
       <c r="Q30" s="8">
-        <v>-20.100000000000001</v>
+        <v>-24.2</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="C31" s="7">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="D31" s="7">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="E31" s="7">
         <v>13.6</v>
       </c>
-      <c r="D31" s="7">
-        <v>14.85</v>
-      </c>
-      <c r="E31" s="7">
-        <v>12.8</v>
-      </c>
       <c r="F31" s="10">
-        <v>0.4</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="G31" s="10">
-        <v>3.03</v>
+        <v>136.76</v>
       </c>
       <c r="H31" s="9">
-        <v>5.42</v>
-      </c>
-      <c r="I31" s="10">
-        <v>3.8</v>
+        <v>3.73</v>
+      </c>
+      <c r="I31" s="8">
+        <v>-31.3</v>
       </c>
       <c r="J31" s="8">
-        <v>-10.9</v>
+        <v>-39.9</v>
       </c>
       <c r="K31" s="9">
-        <v>26.75</v>
+        <v>30.48</v>
       </c>
       <c r="L31" s="8">
-        <v>-16.3</v>
+        <v>-20.100000000000001</v>
       </c>
       <c r="M31" s="9">
-        <v>5.42</v>
-      </c>
-      <c r="N31" s="10">
-        <v>3.8</v>
+        <v>3.73</v>
+      </c>
+      <c r="N31" s="8">
+        <v>-31.3</v>
       </c>
       <c r="O31" s="8">
-        <v>-10.9</v>
+        <v>-39.9</v>
       </c>
       <c r="P31" s="9">
-        <v>26.75</v>
+        <v>30.48</v>
       </c>
       <c r="Q31" s="8">
-        <v>-16.3</v>
+        <v>-20.100000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>10.85</v>
+        <v>13.2</v>
       </c>
       <c r="C32" s="7">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="D32" s="7">
-        <v>13.45</v>
+        <v>14.85</v>
       </c>
       <c r="E32" s="7">
-        <v>10.55</v>
+        <v>12.8</v>
       </c>
       <c r="F32" s="10">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="G32" s="10">
-        <v>18.920000000000002</v>
+        <v>3.03</v>
       </c>
       <c r="H32" s="9">
-        <v>5.22</v>
-      </c>
-      <c r="I32" s="8">
-        <v>-21.5</v>
+        <v>5.42</v>
+      </c>
+      <c r="I32" s="10">
+        <v>3.8</v>
       </c>
       <c r="J32" s="8">
-        <v>-18.100000000000001</v>
+        <v>-10.9</v>
       </c>
       <c r="K32" s="9">
-        <v>21.33</v>
+        <v>26.75</v>
       </c>
       <c r="L32" s="8">
-        <v>-17.600000000000001</v>
+        <v>-16.3</v>
       </c>
       <c r="M32" s="9">
-        <v>5.22</v>
-      </c>
-      <c r="N32" s="8">
-        <v>-21.5</v>
+        <v>5.42</v>
+      </c>
+      <c r="N32" s="10">
+        <v>3.8</v>
       </c>
       <c r="O32" s="8">
-        <v>-18.100000000000001</v>
+        <v>-10.9</v>
       </c>
       <c r="P32" s="9">
-        <v>21.33</v>
+        <v>26.75</v>
       </c>
       <c r="Q32" s="8">
-        <v>-17.600000000000001</v>
+        <v>-16.3</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>15.65</v>
+        <v>10.85</v>
       </c>
       <c r="C33" s="7">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="D33" s="7">
-        <v>16.5</v>
+        <v>13.45</v>
       </c>
       <c r="E33" s="7">
-        <v>9.09</v>
-      </c>
-      <c r="F33" s="8">
-        <v>-4.9000000000000004</v>
-      </c>
-      <c r="G33" s="8">
-        <v>-30.63</v>
+        <v>10.55</v>
+      </c>
+      <c r="F33" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="G33" s="10">
+        <v>18.920000000000002</v>
       </c>
       <c r="H33" s="9">
-        <v>6.65</v>
-      </c>
-      <c r="I33" s="10">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="J33" s="10">
-        <v>10.5</v>
+        <v>5.22</v>
+      </c>
+      <c r="I33" s="8">
+        <v>-21.5</v>
+      </c>
+      <c r="J33" s="8">
+        <v>-18.100000000000001</v>
       </c>
       <c r="K33" s="9">
-        <v>16.11</v>
+        <v>21.33</v>
       </c>
       <c r="L33" s="8">
-        <v>-17.399999999999999</v>
+        <v>-17.600000000000001</v>
       </c>
       <c r="M33" s="9">
-        <v>6.65</v>
-      </c>
-      <c r="N33" s="10">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="O33" s="10">
-        <v>10.5</v>
+        <v>5.22</v>
+      </c>
+      <c r="N33" s="8">
+        <v>-21.5</v>
+      </c>
+      <c r="O33" s="8">
+        <v>-18.100000000000001</v>
       </c>
       <c r="P33" s="9">
-        <v>16.11</v>
+        <v>21.33</v>
       </c>
       <c r="Q33" s="8">
-        <v>-17.399999999999999</v>
+        <v>-17.600000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>17.149999999999999</v>
+        <v>15.65</v>
       </c>
       <c r="C34" s="7">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="D34" s="7">
-        <v>17.600000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="E34" s="7">
-        <v>15.95</v>
+        <v>9.09</v>
       </c>
       <c r="F34" s="8">
-        <v>-1.5</v>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="G34" s="8">
-        <v>-8.57</v>
+        <v>-30.63</v>
       </c>
       <c r="H34" s="9">
-        <v>3.77</v>
-      </c>
-      <c r="I34" s="8">
-        <v>-33.700000000000003</v>
-      </c>
-      <c r="J34" s="8">
-        <v>-26.8</v>
+        <v>6.65</v>
+      </c>
+      <c r="I34" s="10">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="J34" s="10">
+        <v>10.5</v>
       </c>
       <c r="K34" s="9">
-        <v>9.4600000000000009</v>
+        <v>16.11</v>
       </c>
       <c r="L34" s="8">
-        <v>-29.8</v>
+        <v>-17.399999999999999</v>
       </c>
       <c r="M34" s="9">
-        <v>3.77</v>
-      </c>
-      <c r="N34" s="8">
-        <v>-33.700000000000003</v>
-      </c>
-      <c r="O34" s="8">
-        <v>-26.8</v>
+        <v>6.65</v>
+      </c>
+      <c r="N34" s="10">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="O34" s="10">
+        <v>10.5</v>
       </c>
       <c r="P34" s="9">
-        <v>9.4600000000000009</v>
+        <v>16.11</v>
       </c>
       <c r="Q34" s="8">
-        <v>-29.8</v>
+        <v>-17.399999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>20.65</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="C35" s="7">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="D35" s="7">
-        <v>21.05</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E35" s="7">
-        <v>17.2</v>
+        <v>15.95</v>
       </c>
       <c r="F35" s="8">
-        <v>-3.1</v>
+        <v>-1.5</v>
       </c>
       <c r="G35" s="8">
-        <v>-15.05</v>
+        <v>-8.57</v>
       </c>
       <c r="H35" s="9">
-        <v>5.69</v>
+        <v>3.77</v>
       </c>
       <c r="I35" s="8">
-        <v>-8.9</v>
+        <v>-33.700000000000003</v>
       </c>
       <c r="J35" s="8">
-        <v>-31.7</v>
+        <v>-26.8</v>
       </c>
       <c r="K35" s="9">
-        <v>5.69</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="L35" s="8">
-        <v>-31.7</v>
+        <v>-29.8</v>
       </c>
       <c r="M35" s="9">
-        <v>5.69</v>
+        <v>3.77</v>
       </c>
       <c r="N35" s="8">
-        <v>-8.9</v>
+        <v>-33.700000000000003</v>
       </c>
       <c r="O35" s="8">
-        <v>-31.7</v>
+        <v>-26.8</v>
       </c>
       <c r="P35" s="9">
-        <v>5.69</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="Q35" s="8">
-        <v>-31.7</v>
+        <v>-29.8</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7">
-        <v>20.2</v>
+        <v>20.65</v>
       </c>
       <c r="C36" s="7">
-        <v>20.6</v>
+        <v>17.5</v>
       </c>
       <c r="D36" s="7">
-        <v>21.4</v>
+        <v>21.05</v>
       </c>
       <c r="E36" s="7">
-        <v>19.95</v>
-      </c>
-      <c r="F36" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="G36" s="10">
-        <v>1.98</v>
+        <v>17.2</v>
+      </c>
+      <c r="F36" s="8">
+        <v>-3.1</v>
+      </c>
+      <c r="G36" s="8">
+        <v>-15.05</v>
       </c>
       <c r="H36" s="9">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="I36" s="10">
-        <v>14.8</v>
-      </c>
-      <c r="J36" s="10">
-        <v>25.5</v>
+        <v>5.69</v>
+      </c>
+      <c r="I36" s="8">
+        <v>-8.9</v>
+      </c>
+      <c r="J36" s="8">
+        <v>-31.7</v>
       </c>
       <c r="K36" s="9">
-        <v>88.31</v>
-      </c>
-      <c r="L36" s="10">
-        <v>297.10000000000002</v>
+        <v>5.69</v>
+      </c>
+      <c r="L36" s="8">
+        <v>-31.7</v>
       </c>
       <c r="M36" s="9">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="N36" s="10">
-        <v>14.8</v>
-      </c>
-      <c r="O36" s="10">
-        <v>25.5</v>
+        <v>5.69</v>
+      </c>
+      <c r="N36" s="8">
+        <v>-8.9</v>
+      </c>
+      <c r="O36" s="8">
+        <v>-31.7</v>
       </c>
       <c r="P36" s="9">
-        <v>88.31</v>
-      </c>
-      <c r="Q36" s="10">
-        <v>297.10000000000002</v>
+        <v>5.69</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>-31.7</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7">
-        <v>21.15</v>
+        <v>20.2</v>
       </c>
       <c r="C37" s="7">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="D37" s="7">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="E37" s="7">
-        <v>20.05</v>
-      </c>
-      <c r="F37" s="8">
-        <v>-0.95</v>
-      </c>
-      <c r="G37" s="8">
-        <v>-4.49</v>
+        <v>19.95</v>
+      </c>
+      <c r="F37" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="G37" s="10">
+        <v>1.98</v>
       </c>
       <c r="H37" s="9">
-        <v>8.11</v>
-      </c>
-      <c r="I37" s="8">
-        <v>-8.56</v>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I37" s="10">
+        <v>14.8</v>
       </c>
       <c r="J37" s="10">
-        <v>10.6</v>
+        <v>25.5</v>
       </c>
       <c r="K37" s="9">
-        <v>79</v>
+        <v>88.31</v>
       </c>
       <c r="L37" s="10">
-        <v>432.8</v>
+        <v>297.10000000000002</v>
       </c>
       <c r="M37" s="9">
-        <v>8.11</v>
-      </c>
-      <c r="N37" s="8">
-        <v>-8.56</v>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N37" s="10">
+        <v>14.8</v>
       </c>
       <c r="O37" s="10">
-        <v>10.6</v>
+        <v>25.5</v>
       </c>
       <c r="P37" s="9">
-        <v>79</v>
+        <v>88.31</v>
       </c>
       <c r="Q37" s="10">
-        <v>432.8</v>
+        <v>297.10000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7">
-        <v>20.149999999999999</v>
+        <v>21.15</v>
       </c>
       <c r="C38" s="7">
-        <v>21.15</v>
+        <v>20.2</v>
       </c>
       <c r="D38" s="7">
-        <v>22.35</v>
+        <v>21.6</v>
       </c>
       <c r="E38" s="7">
-        <v>19.75</v>
-      </c>
-      <c r="F38" s="10">
-        <v>1</v>
-      </c>
-      <c r="G38" s="10">
-        <v>4.96</v>
+        <v>20.05</v>
+      </c>
+      <c r="F38" s="8">
+        <v>-0.95</v>
+      </c>
+      <c r="G38" s="8">
+        <v>-4.49</v>
       </c>
       <c r="H38" s="9">
-        <v>8.8699999999999992</v>
+        <v>8.11</v>
       </c>
       <c r="I38" s="8">
-        <v>-19.899999999999999</v>
+        <v>-8.56</v>
       </c>
       <c r="J38" s="10">
-        <v>18.2</v>
+        <v>10.6</v>
       </c>
       <c r="K38" s="9">
-        <v>70.900000000000006</v>
+        <v>79</v>
       </c>
       <c r="L38" s="10">
-        <v>845.4</v>
+        <v>432.8</v>
       </c>
       <c r="M38" s="9">
-        <v>8.8699999999999992</v>
+        <v>8.11</v>
       </c>
       <c r="N38" s="8">
-        <v>-19.899999999999999</v>
+        <v>-8.56</v>
       </c>
       <c r="O38" s="10">
-        <v>18.2</v>
+        <v>10.6</v>
       </c>
       <c r="P38" s="9">
-        <v>70.900000000000006</v>
+        <v>79</v>
       </c>
       <c r="Q38" s="10">
-        <v>845.4</v>
+        <v>432.8</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7">
-        <v>20.3</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="C39" s="7">
-        <v>20.149999999999999</v>
+        <v>21.15</v>
       </c>
       <c r="D39" s="7">
-        <v>21.35</v>
+        <v>22.35</v>
       </c>
       <c r="E39" s="7">
-        <v>20</v>
-      </c>
-      <c r="F39" s="8">
-        <v>-0.15</v>
-      </c>
-      <c r="G39" s="8">
-        <v>-0.74</v>
+        <v>19.75</v>
+      </c>
+      <c r="F39" s="10">
+        <v>1</v>
+      </c>
+      <c r="G39" s="10">
+        <v>4.96</v>
       </c>
       <c r="H39" s="9">
-        <v>11.06</v>
-      </c>
-      <c r="I39" s="10">
-        <v>80.400000000000006</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>17</v>
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="I39" s="8">
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="J39" s="10">
+        <v>18.2</v>
       </c>
       <c r="K39" s="9">
-        <v>62.03</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>17</v>
+        <v>70.900000000000006</v>
+      </c>
+      <c r="L39" s="10">
+        <v>845.4</v>
       </c>
       <c r="M39" s="9">
-        <v>11.06</v>
-      </c>
-      <c r="N39" s="10">
-        <v>80.400000000000006</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>17</v>
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="N39" s="8">
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="O39" s="10">
+        <v>18.2</v>
       </c>
       <c r="P39" s="9">
-        <v>62.03</v>
-      </c>
-      <c r="Q39" s="9" t="s">
-        <v>17</v>
+        <v>70.900000000000006</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>845.4</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7">
-        <v>24.15</v>
+        <v>20.3</v>
       </c>
       <c r="C40" s="7">
-        <v>20.3</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="D40" s="7">
-        <v>24.35</v>
+        <v>21.35</v>
       </c>
       <c r="E40" s="7">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="F40" s="8">
-        <v>-4.0999999999999996</v>
+        <v>-0.15</v>
       </c>
       <c r="G40" s="8">
-        <v>-16.8</v>
+        <v>-0.74</v>
       </c>
       <c r="H40" s="9">
-        <v>6.13</v>
-      </c>
-      <c r="I40" s="8">
-        <v>-8.08</v>
+        <v>11.06</v>
+      </c>
+      <c r="I40" s="10">
+        <v>80.400000000000006</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K40" s="9">
-        <v>50.97</v>
+        <v>62.03</v>
       </c>
       <c r="L40" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M40" s="9">
-        <v>6.13</v>
-      </c>
-      <c r="N40" s="8">
-        <v>-8.08</v>
+        <v>11.06</v>
+      </c>
+      <c r="N40" s="10">
+        <v>80.400000000000006</v>
       </c>
       <c r="O40" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P40" s="9">
-        <v>50.97</v>
+        <v>62.03</v>
       </c>
       <c r="Q40" s="9" t="s">
         <v>17</v>
@@ -3287,52 +3295,52 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7">
-        <v>22.05</v>
+        <v>24.15</v>
       </c>
       <c r="C41" s="7">
-        <v>24.4</v>
+        <v>20.3</v>
       </c>
       <c r="D41" s="7">
-        <v>25.2</v>
+        <v>24.35</v>
       </c>
       <c r="E41" s="7">
-        <v>21.85</v>
-      </c>
-      <c r="F41" s="10">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="G41" s="10">
-        <v>11.16</v>
+        <v>19.7</v>
+      </c>
+      <c r="F41" s="8">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="G41" s="8">
+        <v>-16.8</v>
       </c>
       <c r="H41" s="9">
-        <v>6.67</v>
-      </c>
-      <c r="I41" s="10">
-        <v>7.61</v>
+        <v>6.13</v>
+      </c>
+      <c r="I41" s="8">
+        <v>-8.08</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K41" s="9">
-        <v>44.83</v>
+        <v>50.97</v>
       </c>
       <c r="L41" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M41" s="9">
-        <v>6.67</v>
-      </c>
-      <c r="N41" s="10">
-        <v>7.61</v>
+        <v>6.13</v>
+      </c>
+      <c r="N41" s="8">
+        <v>-8.08</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P41" s="9">
-        <v>44.83</v>
+        <v>50.97</v>
       </c>
       <c r="Q41" s="9" t="s">
         <v>17</v>
@@ -3340,52 +3348,52 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7">
-        <v>21.5</v>
+        <v>22.05</v>
       </c>
       <c r="C42" s="7">
-        <v>21.95</v>
+        <v>24.4</v>
       </c>
       <c r="D42" s="7">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="E42" s="7">
-        <v>20.65</v>
+        <v>21.85</v>
       </c>
       <c r="F42" s="10">
-        <v>0.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G42" s="10">
-        <v>2.09</v>
+        <v>11.16</v>
       </c>
       <c r="H42" s="9">
-        <v>6.2</v>
+        <v>6.67</v>
       </c>
       <c r="I42" s="10">
-        <v>1.94</v>
+        <v>7.61</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K42" s="9">
-        <v>38.159999999999997</v>
+        <v>44.83</v>
       </c>
       <c r="L42" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M42" s="9">
-        <v>6.2</v>
+        <v>6.67</v>
       </c>
       <c r="N42" s="10">
-        <v>1.94</v>
+        <v>7.61</v>
       </c>
       <c r="O42" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P42" s="9">
-        <v>38.159999999999997</v>
+        <v>44.83</v>
       </c>
       <c r="Q42" s="9" t="s">
         <v>17</v>
@@ -3393,52 +3401,52 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7">
-        <v>24.35</v>
+        <v>21.5</v>
       </c>
       <c r="C43" s="7">
-        <v>21.5</v>
+        <v>21.95</v>
       </c>
       <c r="D43" s="7">
-        <v>25.2</v>
+        <v>22.4</v>
       </c>
       <c r="E43" s="7">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="F43" s="8">
-        <v>-2.85</v>
-      </c>
-      <c r="G43" s="8">
-        <v>-11.7</v>
+        <v>20.65</v>
+      </c>
+      <c r="F43" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="G43" s="10">
+        <v>2.09</v>
       </c>
       <c r="H43" s="9">
-        <v>6.08</v>
-      </c>
-      <c r="I43" s="8">
-        <v>-4.6500000000000004</v>
+        <v>6.2</v>
+      </c>
+      <c r="I43" s="10">
+        <v>1.94</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K43" s="9">
-        <v>31.96</v>
+        <v>38.159999999999997</v>
       </c>
       <c r="L43" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M43" s="9">
-        <v>6.08</v>
-      </c>
-      <c r="N43" s="8">
-        <v>-4.6500000000000004</v>
+        <v>6.2</v>
+      </c>
+      <c r="N43" s="10">
+        <v>1.94</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P43" s="9">
-        <v>31.96</v>
+        <v>38.159999999999997</v>
       </c>
       <c r="Q43" s="9" t="s">
         <v>17</v>
@@ -3446,52 +3454,52 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7">
-        <v>26.7</v>
+        <v>24.35</v>
       </c>
       <c r="C44" s="7">
-        <v>24.35</v>
+        <v>21.5</v>
       </c>
       <c r="D44" s="7">
-        <v>26.7</v>
+        <v>25.2</v>
       </c>
       <c r="E44" s="7">
-        <v>24.3</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="F44" s="8">
-        <v>-1.25</v>
+        <v>-2.85</v>
       </c>
       <c r="G44" s="8">
-        <v>-4.88</v>
+        <v>-11.7</v>
       </c>
       <c r="H44" s="9">
-        <v>6.38</v>
-      </c>
-      <c r="I44" s="10">
-        <v>5.89</v>
+        <v>6.08</v>
+      </c>
+      <c r="I44" s="8">
+        <v>-4.6500000000000004</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K44" s="9">
-        <v>25.88</v>
+        <v>31.96</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M44" s="9">
-        <v>6.38</v>
-      </c>
-      <c r="N44" s="10">
-        <v>5.89</v>
+        <v>6.08</v>
+      </c>
+      <c r="N44" s="8">
+        <v>-4.6500000000000004</v>
       </c>
       <c r="O44" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P44" s="9">
-        <v>25.88</v>
+        <v>31.96</v>
       </c>
       <c r="Q44" s="9" t="s">
         <v>17</v>
@@ -3499,52 +3507,52 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7">
-        <v>20.9</v>
+        <v>26.7</v>
       </c>
       <c r="C45" s="7">
-        <v>25.6</v>
+        <v>24.35</v>
       </c>
       <c r="D45" s="7">
-        <v>27.7</v>
+        <v>26.7</v>
       </c>
       <c r="E45" s="7">
-        <v>20.5</v>
-      </c>
-      <c r="F45" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="G45" s="10">
-        <v>23.08</v>
+        <v>24.3</v>
+      </c>
+      <c r="F45" s="8">
+        <v>-1.25</v>
+      </c>
+      <c r="G45" s="8">
+        <v>-4.88</v>
       </c>
       <c r="H45" s="9">
-        <v>6.02</v>
+        <v>6.38</v>
       </c>
       <c r="I45" s="10">
-        <v>17</v>
+        <v>5.89</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K45" s="9">
-        <v>19.5</v>
+        <v>25.88</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M45" s="9">
-        <v>6.02</v>
+        <v>6.38</v>
       </c>
       <c r="N45" s="10">
-        <v>17</v>
+        <v>5.89</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P45" s="9">
-        <v>19.5</v>
+        <v>25.88</v>
       </c>
       <c r="Q45" s="9" t="s">
         <v>17</v>
@@ -3552,52 +3560,52 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="C46" s="7">
-        <v>20.8</v>
+        <v>25.6</v>
       </c>
       <c r="D46" s="7">
-        <v>21.9</v>
+        <v>27.7</v>
       </c>
       <c r="E46" s="7">
-        <v>18.899999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="F46" s="10">
-        <v>1.85</v>
+        <v>4.8</v>
       </c>
       <c r="G46" s="10">
-        <v>9.76</v>
+        <v>23.08</v>
       </c>
       <c r="H46" s="9">
-        <v>5.15</v>
-      </c>
-      <c r="I46" s="8">
-        <v>-38.200000000000003</v>
+        <v>6.02</v>
+      </c>
+      <c r="I46" s="10">
+        <v>17</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K46" s="9">
-        <v>13.48</v>
+        <v>19.5</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M46" s="9">
-        <v>5.15</v>
-      </c>
-      <c r="N46" s="8">
-        <v>-38.200000000000003</v>
+        <v>6.02</v>
+      </c>
+      <c r="N46" s="10">
+        <v>17</v>
       </c>
       <c r="O46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P46" s="9">
-        <v>13.48</v>
+        <v>19.5</v>
       </c>
       <c r="Q46" s="9" t="s">
         <v>17</v>
@@ -3605,52 +3613,52 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7">
-        <v>19.899999999999999</v>
+        <v>19</v>
       </c>
       <c r="C47" s="7">
-        <v>18.95</v>
+        <v>20.8</v>
       </c>
       <c r="D47" s="7">
-        <v>19.899999999999999</v>
+        <v>21.9</v>
       </c>
       <c r="E47" s="7">
-        <v>18.3</v>
-      </c>
-      <c r="F47" s="8">
-        <v>-0.15</v>
-      </c>
-      <c r="G47" s="8">
-        <v>-0.79</v>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="F47" s="10">
+        <v>1.85</v>
+      </c>
+      <c r="G47" s="10">
+        <v>9.76</v>
       </c>
       <c r="H47" s="9">
-        <v>8.33</v>
-      </c>
-      <c r="I47" s="10">
-        <v>12.4</v>
+        <v>5.15</v>
+      </c>
+      <c r="I47" s="8">
+        <v>-38.200000000000003</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K47" s="9">
-        <v>8.33</v>
+        <v>13.48</v>
       </c>
       <c r="L47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M47" s="9">
-        <v>8.33</v>
-      </c>
-      <c r="N47" s="10">
-        <v>12.4</v>
+        <v>5.15</v>
+      </c>
+      <c r="N47" s="8">
+        <v>-38.200000000000003</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P47" s="9">
-        <v>8.33</v>
+        <v>13.48</v>
       </c>
       <c r="Q47" s="9" t="s">
         <v>17</v>
@@ -3658,52 +3666,52 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7">
-        <v>23</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="C48" s="7">
-        <v>19.100000000000001</v>
+        <v>18.95</v>
       </c>
       <c r="D48" s="7">
-        <v>23.25</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E48" s="7">
-        <v>18.55</v>
+        <v>18.3</v>
       </c>
       <c r="F48" s="8">
-        <v>-2.65</v>
+        <v>-0.15</v>
       </c>
       <c r="G48" s="8">
-        <v>-12.18</v>
+        <v>-0.79</v>
       </c>
       <c r="H48" s="9">
-        <v>7.41</v>
+        <v>8.33</v>
       </c>
       <c r="I48" s="10">
-        <v>1.1299999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="J48" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K48" s="9">
-        <v>22.24</v>
+        <v>8.33</v>
       </c>
       <c r="L48" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M48" s="9">
-        <v>7.41</v>
+        <v>8.33</v>
       </c>
       <c r="N48" s="10">
-        <v>1.1299999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="O48" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P48" s="9">
-        <v>22.24</v>
+        <v>8.33</v>
       </c>
       <c r="Q48" s="9" t="s">
         <v>17</v>
@@ -3711,52 +3719,52 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7">
-        <v>18.149999999999999</v>
+        <v>23</v>
       </c>
       <c r="C49" s="7">
-        <v>21.75</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="D49" s="7">
-        <v>21.75</v>
+        <v>23.25</v>
       </c>
       <c r="E49" s="7">
-        <v>17.55</v>
-      </c>
-      <c r="F49" s="10">
-        <v>3.65</v>
-      </c>
-      <c r="G49" s="10">
-        <v>20.170000000000002</v>
+        <v>18.55</v>
+      </c>
+      <c r="F49" s="8">
+        <v>-2.65</v>
+      </c>
+      <c r="G49" s="8">
+        <v>-12.18</v>
       </c>
       <c r="H49" s="9">
-        <v>7.33</v>
-      </c>
-      <c r="I49" s="8">
-        <v>-2.27</v>
+        <v>7.41</v>
+      </c>
+      <c r="I49" s="10">
+        <v>1.1299999999999999</v>
       </c>
       <c r="J49" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K49" s="9">
-        <v>14.83</v>
+        <v>22.24</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M49" s="9">
-        <v>7.33</v>
-      </c>
-      <c r="N49" s="8">
-        <v>-2.27</v>
+        <v>7.41</v>
+      </c>
+      <c r="N49" s="10">
+        <v>1.1299999999999999</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P49" s="9">
-        <v>14.83</v>
+        <v>22.24</v>
       </c>
       <c r="Q49" s="9" t="s">
         <v>17</v>
@@ -3764,52 +3772,52 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7">
-        <v>34.5</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="C50" s="7">
-        <v>18.100000000000001</v>
+        <v>21.75</v>
       </c>
       <c r="D50" s="7">
-        <v>34.5</v>
+        <v>21.75</v>
       </c>
       <c r="E50" s="7">
-        <v>17.25</v>
-      </c>
-      <c r="F50" s="8">
-        <v>-16.55</v>
-      </c>
-      <c r="G50" s="8">
-        <v>-47.76</v>
+        <v>17.55</v>
+      </c>
+      <c r="F50" s="10">
+        <v>3.65</v>
+      </c>
+      <c r="G50" s="10">
+        <v>20.170000000000002</v>
       </c>
       <c r="H50" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>17</v>
+        <v>7.33</v>
+      </c>
+      <c r="I50" s="8">
+        <v>-2.27</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K50" s="9">
-        <v>7.5</v>
+        <v>14.83</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M50" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="N50" s="9" t="s">
-        <v>17</v>
+        <v>7.33</v>
+      </c>
+      <c r="N50" s="8">
+        <v>-2.27</v>
       </c>
       <c r="O50" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P50" s="9">
-        <v>7.5</v>
+        <v>14.83</v>
       </c>
       <c r="Q50" s="9" t="s">
         <v>17</v>
@@ -3817,54 +3825,107 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
+        <v>43374</v>
+      </c>
+      <c r="B51" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="C51" s="7">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D51" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="E51" s="7">
+        <v>17.25</v>
+      </c>
+      <c r="F51" s="8">
+        <v>-16.55</v>
+      </c>
+      <c r="G51" s="8">
+        <v>-47.76</v>
+      </c>
+      <c r="H51" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P51" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="Q51" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
         <v>43344</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="9">
+      <c r="B52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="9">
         <v>0</v>
       </c>
-      <c r="I51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K51" s="9">
+      <c r="I52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="9">
         <v>0</v>
       </c>
-      <c r="L51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M51" s="9">
+      <c r="L52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" s="9">
         <v>0</v>
       </c>
-      <c r="N51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P51" s="9">
+      <c r="N52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P52" s="9">
         <v>0</v>
       </c>
-      <c r="Q51" s="9" t="s">
+      <c r="Q52" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3883,7 +3944,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>